--- a/3_simulators/data/ttj_s2_raw_data_variables_explained.xlsx
+++ b/3_simulators/data/ttj_s2_raw_data_variables_explained.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\Github_Mannheim\time_to_jump\3_simulators\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AFBA86C-408D-4EFE-AA34-57DC3D3D9410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E504C23-1305-43CC-A88E-1FB7747EC130}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31545" yWindow="2370" windowWidth="20205" windowHeight="13215" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="s2_brightness_discrimination" sheetId="3" r:id="rId1"/>
@@ -64,9 +64,6 @@
     <t>rt</t>
   </si>
   <si>
-    <t>Response time, measured in milliseconds.</t>
-  </si>
-  <si>
     <t>strategy</t>
   </si>
   <si>
@@ -208,6 +205,9 @@
   </si>
   <si>
     <t xml:space="preserve">Scores for the items of German version of the Ruminative Thought Style Questionnaire (RTS-D; Helmig et al., 2016). </t>
+  </si>
+  <si>
+    <t>Response time, measured in seconds.</t>
   </si>
 </sst>
 </file>
@@ -571,13 +571,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9131381-99D7-402F-A28E-05FA861B73BA}">
   <dimension ref="A1:B31"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="75.7109375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="19.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="75.6640625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -585,55 +585,55 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B4" s="2" t="s">
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
@@ -641,23 +641,23 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B9" s="2" t="s">
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+      <c r="B10" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
@@ -665,15 +665,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
@@ -681,148 +681,148 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" ht="60" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
+      <c r="B15" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="60" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B16" s="2" t="s">
+      <c r="B17" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
+      <c r="B25" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B25" s="2" t="s">
+      <c r="B26" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A30" s="5" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" ht="60" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A30" s="5" t="s">
+      <c r="B30" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B30" s="2" t="s">
+    </row>
+    <row r="31" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
+      <c r="B31" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>61</v>
       </c>
     </row>
   </sheetData>
